--- a/jogos_2025-05-21.xlsx
+++ b/jogos_2025-05-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="119">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -271,12 +217,12 @@
     <t>Falkenberg</t>
   </si>
   <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
     <t>Örgryte</t>
   </si>
   <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
     <t>Al Wahda</t>
   </si>
   <si>
@@ -289,12 +235,12 @@
     <t>Atlético Tembetary</t>
   </si>
   <si>
+    <t>Sportivo Ameliano</t>
+  </si>
+  <si>
     <t>Olimpia</t>
   </si>
   <si>
-    <t>Sportivo Ameliano</t>
-  </si>
-  <si>
     <t>Vissel Kobe</t>
   </si>
   <si>
@@ -325,12 +271,12 @@
     <t>Trelleborg</t>
   </si>
   <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
     <t>Sandviken</t>
   </si>
   <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
     <t>Al Hilal</t>
   </si>
   <si>
@@ -343,16 +289,88 @@
     <t>Guaraní</t>
   </si>
   <si>
+    <t>Cerro Porteño</t>
+  </si>
+  <si>
     <t>Libertad</t>
   </si>
   <si>
-    <t>Cerro Porteño</t>
-  </si>
-  <si>
-    <t>incomplete</t>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>['43']</t>
+  </si>
+  <si>
+    <t>['45+2', '86']</t>
+  </si>
+  <si>
+    <t>['78']</t>
+  </si>
+  <si>
+    <t>['56', '70', '89']</t>
+  </si>
+  <si>
+    <t>['-1']</t>
+  </si>
+  <si>
+    <t>['75', '90+7']</t>
+  </si>
+  <si>
+    <t>['45+1', '82']</t>
+  </si>
+  <si>
+    <t>['19', '23', '38', '58']</t>
+  </si>
+  <si>
+    <t>['4', '30', '67', '86']</t>
+  </si>
+  <si>
+    <t>['70']</t>
+  </si>
+  <si>
+    <t>['6', '45+1', '46', '90+2']</t>
+  </si>
+  <si>
+    <t>['51']</t>
+  </si>
+  <si>
+    <t>['34', '58']</t>
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
+  </si>
+  <si>
+    <t>['54']</t>
+  </si>
+  <si>
+    <t>['19', '51']</t>
+  </si>
+  <si>
+    <t>['42', '90+4']</t>
+  </si>
+  <si>
+    <t>['90']</t>
+  </si>
+  <si>
+    <t>['-1', '-1']</t>
+  </si>
+  <si>
+    <t>['5', '7', '53', '66']</t>
+  </si>
+  <si>
+    <t>['77']</t>
+  </si>
+  <si>
+    <t>['49', '61']</t>
+  </si>
+  <si>
+    <t>['28', '78']</t>
+  </si>
+  <si>
+    <t>['9']</t>
   </si>
 </sst>
 </file>
@@ -716,10 +734,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD19"/>
+  <dimension ref="A1:AL19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -834,94 +852,40 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45798</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" t="s">
         <v>75</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
         <v>93</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>111</v>
       </c>
       <c r="L2">
         <v>3.23</v>
@@ -996,102 +960,48 @@
         <v>1.1</v>
       </c>
       <c r="AJ2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL2">
-        <v>1.77</v>
-      </c>
-      <c r="AM2">
-        <v>1.25</v>
-      </c>
-      <c r="AN2">
-        <v>1.28</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>1.18</v>
-      </c>
-      <c r="AQ2">
-        <v>1.37</v>
-      </c>
-      <c r="AR2">
-        <v>1.68</v>
-      </c>
-      <c r="AS2">
-        <v>2.09</v>
-      </c>
-      <c r="AT2">
-        <v>2.7</v>
-      </c>
-      <c r="AU2">
-        <v>3.9</v>
-      </c>
-      <c r="AV2">
-        <v>2.75</v>
-      </c>
-      <c r="AW2">
-        <v>2.06</v>
-      </c>
-      <c r="AX2">
-        <v>1.63</v>
-      </c>
-      <c r="AY2">
-        <v>1.36</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>2.4</v>
-      </c>
-      <c r="BC2">
-        <v>1.62</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>110</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45798.29166666666</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45798</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" t="s">
         <v>76</v>
       </c>
-      <c r="F3" t="s">
-        <v>94</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L3">
         <v>2.03</v>
@@ -1166,93 +1076,39 @@
         <v>1.1</v>
       </c>
       <c r="AJ3" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="AK3" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL3">
-        <v>1.28</v>
-      </c>
-      <c r="AM3">
-        <v>1.25</v>
-      </c>
-      <c r="AN3">
-        <v>1.77</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>1.2</v>
-      </c>
-      <c r="AQ3">
-        <v>1.41</v>
-      </c>
-      <c r="AR3">
-        <v>1.73</v>
-      </c>
-      <c r="AS3">
-        <v>2.17</v>
-      </c>
-      <c r="AT3">
-        <v>2.83</v>
-      </c>
-      <c r="AU3">
-        <v>3.72</v>
-      </c>
-      <c r="AV3">
-        <v>2.6</v>
-      </c>
-      <c r="AW3">
-        <v>1.99</v>
-      </c>
-      <c r="AX3">
-        <v>1.58</v>
-      </c>
-      <c r="AY3">
-        <v>1.33</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.62</v>
-      </c>
-      <c r="BC3">
-        <v>2.5</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>111</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45798.29166666666</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45798</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" t="s">
         <v>77</v>
       </c>
-      <c r="F4" t="s">
-        <v>95</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1261,16 +1117,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L4">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="M4">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="N4">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
         <v>2.15</v>
@@ -1285,13 +1141,13 @@
         <v>1.56</v>
       </c>
       <c r="S4">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="T4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U4">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -1306,22 +1162,22 @@
         <v>6</v>
       </c>
       <c r="Z4">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA4">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="AB4">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AC4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AD4">
         <v>4.8</v>
       </c>
       <c r="AE4">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
         <v>2.1</v>
@@ -1336,90 +1192,36 @@
         <v>1</v>
       </c>
       <c r="AJ4" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="AK4" t="s">
         <v>112</v>
       </c>
-      <c r="AL4">
-        <v>1.4</v>
-      </c>
-      <c r="AM4">
-        <v>1.34</v>
-      </c>
-      <c r="AN4">
-        <v>1.5</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>1.5</v>
-      </c>
-      <c r="AQ4">
-        <v>1.88</v>
-      </c>
-      <c r="AR4">
-        <v>2.38</v>
-      </c>
-      <c r="AS4">
-        <v>3.42</v>
-      </c>
-      <c r="AT4">
-        <v>4</v>
-      </c>
-      <c r="AU4">
-        <v>2.4</v>
-      </c>
-      <c r="AV4">
-        <v>1.91</v>
-      </c>
-      <c r="AW4">
-        <v>1.57</v>
-      </c>
-      <c r="AX4">
-        <v>1.33</v>
-      </c>
-      <c r="AY4">
-        <v>1.2</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>2.15</v>
-      </c>
-      <c r="BC4">
-        <v>2.06</v>
-      </c>
-      <c r="BD4" s="3">
+      <c r="AL4" s="3">
         <v>45798.39583333334</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45798</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
         <v>78</v>
       </c>
-      <c r="F5" t="s">
-        <v>96</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1431,16 +1233,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L5">
         <v>2.38</v>
       </c>
       <c r="M5">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N5">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="O5">
         <v>1.95</v>
@@ -1452,147 +1254,93 @@
         <v>2.05</v>
       </c>
       <c r="R5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T5">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="U5">
         <v>1.5</v>
       </c>
       <c r="V5">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="W5">
         <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z5">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AA5">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AB5">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC5">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD5">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="AE5">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AF5">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG5">
         <v>2.25</v>
       </c>
       <c r="AH5">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AI5">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AJ5" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="AK5" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL5">
-        <v>1.25</v>
-      </c>
-      <c r="AM5">
-        <v>1.25</v>
-      </c>
-      <c r="AN5">
-        <v>1.57</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>1.26</v>
-      </c>
-      <c r="AQ5">
-        <v>1.41</v>
-      </c>
-      <c r="AR5">
-        <v>2.02</v>
-      </c>
-      <c r="AS5">
-        <v>2.36</v>
-      </c>
-      <c r="AT5">
-        <v>3</v>
-      </c>
-      <c r="AU5">
-        <v>3.8</v>
-      </c>
-      <c r="AV5">
-        <v>2.48</v>
-      </c>
-      <c r="AW5">
-        <v>1.92</v>
-      </c>
-      <c r="AX5">
-        <v>1.54</v>
-      </c>
-      <c r="AY5">
-        <v>1.31</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.95</v>
-      </c>
-      <c r="BC5">
-        <v>2.05</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>107</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45798.5</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45798</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" t="s">
         <v>79</v>
       </c>
-      <c r="F6" t="s">
-        <v>97</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1601,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L6">
         <v>2.03</v>
@@ -1676,93 +1424,39 @@
         <v>1.07</v>
       </c>
       <c r="AJ6" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL6">
-        <v>1.33</v>
-      </c>
-      <c r="AM6">
-        <v>1.3</v>
-      </c>
-      <c r="AN6">
-        <v>1.65</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.67</v>
-      </c>
-      <c r="BC6">
-        <v>2.6</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>98</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45798.5</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45798</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" t="s">
         <v>80</v>
       </c>
-      <c r="F7" t="s">
-        <v>98</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1771,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L7">
         <v>3.2</v>
@@ -1846,90 +1540,36 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="AK7" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>2.5</v>
-      </c>
-      <c r="BC7">
-        <v>1.73</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>113</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45798.54166666666</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45798</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" t="s">
         <v>81</v>
       </c>
-      <c r="F8" t="s">
-        <v>99</v>
-      </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1941,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L8">
         <v>1.2</v>
@@ -2016,102 +1656,48 @@
         <v>1.44</v>
       </c>
       <c r="AJ8" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="AK8" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL8">
-        <v>1.05</v>
-      </c>
-      <c r="AM8">
-        <v>1.1</v>
-      </c>
-      <c r="AN8">
-        <v>4</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>1.27</v>
-      </c>
-      <c r="AQ8">
-        <v>1.51</v>
-      </c>
-      <c r="AR8">
-        <v>1.89</v>
-      </c>
-      <c r="AS8">
-        <v>2.43</v>
-      </c>
-      <c r="AT8">
-        <v>3.34</v>
-      </c>
-      <c r="AU8">
-        <v>3.14</v>
-      </c>
-      <c r="AV8">
-        <v>2.26</v>
-      </c>
-      <c r="AW8">
-        <v>1.77</v>
-      </c>
-      <c r="AX8">
-        <v>1.44</v>
-      </c>
-      <c r="AY8">
-        <v>1.24</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>1.22</v>
-      </c>
-      <c r="BC8">
-        <v>4</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>107</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45798.54861111111</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45798</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" t="s">
         <v>82</v>
       </c>
-      <c r="F9" t="s">
-        <v>100</v>
-      </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L9">
         <v>2.5</v>
@@ -2186,102 +1772,48 @@
         <v>1.1</v>
       </c>
       <c r="AJ9" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="AK9" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL9">
-        <v>1.42</v>
-      </c>
-      <c r="AM9">
-        <v>1.25</v>
-      </c>
-      <c r="AN9">
-        <v>1.53</v>
-      </c>
-      <c r="AO9">
-        <v>-1</v>
-      </c>
-      <c r="AP9">
-        <v>1.21</v>
-      </c>
-      <c r="AQ9">
-        <v>1.41</v>
-      </c>
-      <c r="AR9">
-        <v>1.75</v>
-      </c>
-      <c r="AS9">
-        <v>2.21</v>
-      </c>
-      <c r="AT9">
-        <v>2.92</v>
-      </c>
-      <c r="AU9">
-        <v>3.58</v>
-      </c>
-      <c r="AV9">
-        <v>2.52</v>
-      </c>
-      <c r="AW9">
-        <v>1.92</v>
-      </c>
-      <c r="AX9">
-        <v>1.53</v>
-      </c>
-      <c r="AY9">
-        <v>1.31</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>1.8</v>
-      </c>
-      <c r="BC9">
-        <v>2.2</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>107</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45798.55902777778</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45798</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" t="s">
         <v>83</v>
       </c>
-      <c r="F10" t="s">
-        <v>101</v>
-      </c>
       <c r="G10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L10">
         <v>2.14</v>
@@ -2356,102 +1888,48 @@
         <v>1.13</v>
       </c>
       <c r="AJ10" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="AK10" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL10">
-        <v>1.38</v>
-      </c>
-      <c r="AM10">
-        <v>1.25</v>
-      </c>
-      <c r="AN10">
-        <v>1.62</v>
-      </c>
-      <c r="AO10">
-        <v>-1</v>
-      </c>
-      <c r="AP10">
-        <v>1.18</v>
-      </c>
-      <c r="AQ10">
-        <v>1.33</v>
-      </c>
-      <c r="AR10">
-        <v>1.54</v>
-      </c>
-      <c r="AS10">
-        <v>1.85</v>
-      </c>
-      <c r="AT10">
-        <v>2.3</v>
-      </c>
-      <c r="AU10">
-        <v>4.1</v>
-      </c>
-      <c r="AV10">
-        <v>2.95</v>
-      </c>
-      <c r="AW10">
-        <v>2.3</v>
-      </c>
-      <c r="AX10">
-        <v>1.83</v>
-      </c>
-      <c r="AY10">
-        <v>1.54</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.85</v>
-      </c>
-      <c r="BC10">
-        <v>2.2</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>114</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45798.58333333334</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45798</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" t="s">
         <v>84</v>
       </c>
-      <c r="F11" t="s">
-        <v>102</v>
-      </c>
       <c r="G11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L11">
         <v>2.17</v>
@@ -2526,90 +2004,36 @@
         <v>1.14</v>
       </c>
       <c r="AJ11" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AK11" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL11">
-        <v>1.4</v>
-      </c>
-      <c r="AM11">
-        <v>1.22</v>
-      </c>
-      <c r="AN11">
-        <v>1.6</v>
-      </c>
-      <c r="AO11">
-        <v>-1</v>
-      </c>
-      <c r="AP11">
-        <v>1.2</v>
-      </c>
-      <c r="AQ11">
-        <v>1.34</v>
-      </c>
-      <c r="AR11">
-        <v>1.56</v>
-      </c>
-      <c r="AS11">
-        <v>1.88</v>
-      </c>
-      <c r="AT11">
-        <v>2.32</v>
-      </c>
-      <c r="AU11">
-        <v>4</v>
-      </c>
-      <c r="AV11">
-        <v>2.9</v>
-      </c>
-      <c r="AW11">
-        <v>2.25</v>
-      </c>
-      <c r="AX11">
-        <v>1.81</v>
-      </c>
-      <c r="AY11">
-        <v>1.52</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>1.85</v>
-      </c>
-      <c r="BC11">
-        <v>2.15</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>107</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45798.58333333334</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45798</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" t="s">
         <v>85</v>
       </c>
-      <c r="F12" t="s">
-        <v>103</v>
-      </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2621,25 +2045,25 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L12">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="M12">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N12">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="O12">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="P12">
         <v>11</v>
       </c>
       <c r="Q12">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="R12">
         <v>1.3</v>
@@ -2648,16 +2072,16 @@
         <v>3.2</v>
       </c>
       <c r="T12">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="U12">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="V12">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1.04</v>
@@ -2666,150 +2090,96 @@
         <v>11</v>
       </c>
       <c r="Z12">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AA12">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AB12">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AC12">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AD12">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AE12">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF12">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AG12">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="AH12">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI12">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AJ12" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL12">
-        <v>1.38</v>
-      </c>
-      <c r="AM12">
-        <v>1.22</v>
-      </c>
-      <c r="AN12">
-        <v>1.62</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>1.21</v>
-      </c>
-      <c r="AQ12">
-        <v>1.36</v>
-      </c>
-      <c r="AR12">
-        <v>1.6</v>
-      </c>
-      <c r="AS12">
-        <v>1.94</v>
-      </c>
-      <c r="AT12">
-        <v>2.4</v>
-      </c>
-      <c r="AU12">
-        <v>3.9</v>
-      </c>
-      <c r="AV12">
-        <v>2.8</v>
-      </c>
-      <c r="AW12">
-        <v>2.17</v>
-      </c>
-      <c r="AX12">
-        <v>1.76</v>
-      </c>
-      <c r="AY12">
-        <v>1.49</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>1.83</v>
-      </c>
-      <c r="BC12">
-        <v>2.15</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>107</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45798.58333333334</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45798</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" t="s">
         <v>86</v>
       </c>
-      <c r="F13" t="s">
-        <v>104</v>
-      </c>
       <c r="G13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L13">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="M13">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N13">
-        <v>4.75</v>
+        <v>2.8</v>
       </c>
       <c r="O13">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="P13">
         <v>11</v>
       </c>
       <c r="Q13">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="R13">
         <v>1.3</v>
@@ -2818,16 +2188,16 @@
         <v>3.2</v>
       </c>
       <c r="T13">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="U13">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
         <v>1.04</v>
@@ -2836,123 +2206,69 @@
         <v>11</v>
       </c>
       <c r="Z13">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AA13">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AB13">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AC13">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AD13">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AE13">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF13">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AH13">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="AI13">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AJ13" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL13">
-        <v>1.15</v>
-      </c>
-      <c r="AM13">
-        <v>1.18</v>
-      </c>
-      <c r="AN13">
-        <v>2.3</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
-      </c>
-      <c r="AP13">
-        <v>1.2</v>
-      </c>
-      <c r="AQ13">
-        <v>1.35</v>
-      </c>
-      <c r="AR13">
-        <v>1.57</v>
-      </c>
-      <c r="AS13">
-        <v>1.9</v>
-      </c>
-      <c r="AT13">
-        <v>2.35</v>
-      </c>
-      <c r="AU13">
-        <v>3.95</v>
-      </c>
-      <c r="AV13">
-        <v>2.9</v>
-      </c>
-      <c r="AW13">
-        <v>2.23</v>
-      </c>
-      <c r="AX13">
-        <v>1.79</v>
-      </c>
-      <c r="AY13">
-        <v>1.5</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.5</v>
-      </c>
-      <c r="BC13">
-        <v>2.9</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>107</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45798.58333333334</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45798</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" t="s">
         <v>87</v>
       </c>
-      <c r="F14" t="s">
-        <v>105</v>
-      </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2961,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L14">
         <v>9.5</v>
@@ -3036,102 +2352,48 @@
         <v>1.44</v>
       </c>
       <c r="AJ14" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="AK14" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL14">
-        <v>3.45</v>
-      </c>
-      <c r="AM14">
-        <v>1.08</v>
-      </c>
-      <c r="AN14">
-        <v>1.07</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>1.21</v>
-      </c>
-      <c r="AQ14">
-        <v>1.4</v>
-      </c>
-      <c r="AR14">
-        <v>1.71</v>
-      </c>
-      <c r="AS14">
-        <v>2.14</v>
-      </c>
-      <c r="AT14">
-        <v>2.83</v>
-      </c>
-      <c r="AU14">
-        <v>3.58</v>
-      </c>
-      <c r="AV14">
-        <v>2.56</v>
-      </c>
-      <c r="AW14">
-        <v>1.97</v>
-      </c>
-      <c r="AX14">
-        <v>1.57</v>
-      </c>
-      <c r="AY14">
-        <v>1.33</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>3.75</v>
-      </c>
-      <c r="BC14">
-        <v>1.25</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>108</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45798.625</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45798</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" t="s">
         <v>88</v>
       </c>
-      <c r="F15" t="s">
-        <v>106</v>
-      </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L15">
         <v>3.35</v>
@@ -3206,93 +2468,39 @@
         <v>1.05</v>
       </c>
       <c r="AJ15" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="AK15" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL15">
-        <v>1.68</v>
-      </c>
-      <c r="AM15">
-        <v>1.32</v>
-      </c>
-      <c r="AN15">
-        <v>1.3</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>1.41</v>
-      </c>
-      <c r="AQ15">
-        <v>1.68</v>
-      </c>
-      <c r="AR15">
-        <v>2.08</v>
-      </c>
-      <c r="AS15">
-        <v>2.65</v>
-      </c>
-      <c r="AT15">
-        <v>3.55</v>
-      </c>
-      <c r="AU15">
-        <v>2.65</v>
-      </c>
-      <c r="AV15">
-        <v>2.02</v>
-      </c>
-      <c r="AW15">
-        <v>1.65</v>
-      </c>
-      <c r="AX15">
-        <v>1.4</v>
-      </c>
-      <c r="AY15">
-        <v>1.24</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>2.38</v>
-      </c>
-      <c r="BC15">
-        <v>1.73</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>115</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45798.64583333334</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45798</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" t="s">
         <v>89</v>
       </c>
-      <c r="F16" t="s">
-        <v>107</v>
-      </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -3301,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L16">
         <v>3.13</v>
@@ -3376,111 +2584,57 @@
         <v>1.02</v>
       </c>
       <c r="AJ16" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="AK16" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL16">
-        <v>1.57</v>
-      </c>
-      <c r="AM16">
-        <v>1.35</v>
-      </c>
-      <c r="AN16">
-        <v>1.34</v>
-      </c>
-      <c r="AO16">
-        <v>-1</v>
-      </c>
-      <c r="AP16">
-        <v>1.38</v>
-      </c>
-      <c r="AQ16">
-        <v>1.67</v>
-      </c>
-      <c r="AR16">
-        <v>2.05</v>
-      </c>
-      <c r="AS16">
-        <v>2.55</v>
-      </c>
-      <c r="AT16">
-        <v>3.4</v>
-      </c>
-      <c r="AU16">
-        <v>2.7</v>
-      </c>
-      <c r="AV16">
-        <v>2.07</v>
-      </c>
-      <c r="AW16">
-        <v>1.68</v>
-      </c>
-      <c r="AX16">
-        <v>1.43</v>
-      </c>
-      <c r="AY16">
-        <v>1.26</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>2.3</v>
-      </c>
-      <c r="BC16">
-        <v>1.8</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>116</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45798.64583333334</v>
       </c>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>45798</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" t="s">
         <v>90</v>
       </c>
-      <c r="F17" t="s">
-        <v>108</v>
-      </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L17">
-        <v>3.09</v>
+        <v>2.6</v>
       </c>
       <c r="M17">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="N17">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="O17">
         <v>2.25</v>
@@ -3492,142 +2646,88 @@
         <v>1.93</v>
       </c>
       <c r="R17">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S17">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="T17">
         <v>3.3</v>
       </c>
       <c r="U17">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V17">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="Z17">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AA17">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AB17">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AC17">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AD17">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AE17">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF17">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG17">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AH17">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AI17">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AJ17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="AK17" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL17">
-        <v>1.55</v>
-      </c>
-      <c r="AM17">
-        <v>1.3</v>
-      </c>
-      <c r="AN17">
-        <v>1.35</v>
-      </c>
-      <c r="AO17">
-        <v>-1</v>
-      </c>
-      <c r="AP17">
-        <v>1.5</v>
-      </c>
-      <c r="AQ17">
-        <v>1.81</v>
-      </c>
-      <c r="AR17">
-        <v>2.8</v>
-      </c>
-      <c r="AS17">
-        <v>3</v>
-      </c>
-      <c r="AT17">
-        <v>4</v>
-      </c>
-      <c r="AU17">
-        <v>2.4</v>
-      </c>
-      <c r="AV17">
-        <v>1.91</v>
-      </c>
-      <c r="AW17">
-        <v>1.55</v>
-      </c>
-      <c r="AX17">
-        <v>1.33</v>
-      </c>
-      <c r="AY17">
-        <v>1.2</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>2.25</v>
-      </c>
-      <c r="BC17">
-        <v>1.93</v>
-      </c>
-      <c r="BD17" s="3">
+        <v>117</v>
+      </c>
+      <c r="AL17" s="3">
         <v>45798.8125</v>
       </c>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:38">
       <c r="A18" s="2">
         <v>45798</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" t="s">
         <v>73</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>91</v>
       </c>
-      <c r="F18" t="s">
-        <v>109</v>
-      </c>
       <c r="G18">
         <v>0</v>
       </c>
@@ -3641,234 +2741,180 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L18">
-        <v>2.65</v>
+        <v>5.31</v>
       </c>
       <c r="M18">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N18">
-        <v>2.42</v>
+        <v>1.69</v>
       </c>
       <c r="O18">
-        <v>2.09</v>
+        <v>2.34</v>
       </c>
       <c r="P18">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="Q18">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="R18">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="S18">
-        <v>2.33</v>
+        <v>2.49</v>
       </c>
       <c r="T18">
-        <v>3.48</v>
+        <v>3.14</v>
       </c>
       <c r="U18">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V18">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="W18">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X18">
         <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="Z18">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AA18">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AB18">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AC18">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AD18">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AE18">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG18">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AH18">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AI18">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AJ18" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="AK18" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL18">
-        <v>1.4</v>
-      </c>
-      <c r="AM18">
-        <v>1.31</v>
-      </c>
-      <c r="AN18">
-        <v>1.44</v>
-      </c>
-      <c r="AO18">
-        <v>-1</v>
-      </c>
-      <c r="AP18">
-        <v>1.55</v>
-      </c>
-      <c r="AQ18">
-        <v>1.89</v>
-      </c>
-      <c r="AR18">
-        <v>2.92</v>
-      </c>
-      <c r="AS18">
-        <v>3.2</v>
-      </c>
-      <c r="AT18">
-        <v>4.33</v>
-      </c>
-      <c r="AU18">
-        <v>2.33</v>
-      </c>
-      <c r="AV18">
-        <v>1.8</v>
-      </c>
-      <c r="AW18">
-        <v>1.5</v>
-      </c>
-      <c r="AX18">
-        <v>1.3</v>
-      </c>
-      <c r="AY18">
-        <v>1.18</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>2.09</v>
-      </c>
-      <c r="BC18">
-        <v>1.97</v>
-      </c>
-      <c r="BD18" s="3">
+        <v>107</v>
+      </c>
+      <c r="AL18" s="3">
         <v>45798.8125</v>
       </c>
     </row>
-    <row r="19" spans="1:56">
+    <row r="19" spans="1:38">
       <c r="A19" s="2">
         <v>45798</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" t="s">
         <v>92</v>
       </c>
-      <c r="F19" t="s">
-        <v>110</v>
-      </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L19">
-        <v>3.13</v>
+        <v>2.41</v>
       </c>
       <c r="M19">
-        <v>3.27</v>
+        <v>2.95</v>
       </c>
       <c r="N19">
-        <v>2.02</v>
+        <v>2.65</v>
       </c>
       <c r="O19">
-        <v>2.34</v>
+        <v>2.09</v>
       </c>
       <c r="P19">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="Q19">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="R19">
+        <v>1.54</v>
+      </c>
+      <c r="S19">
+        <v>2.38</v>
+      </c>
+      <c r="T19">
+        <v>3.5</v>
+      </c>
+      <c r="U19">
+        <v>1.29</v>
+      </c>
+      <c r="V19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>1.07</v>
+      </c>
+      <c r="Y19">
+        <v>6.93</v>
+      </c>
+      <c r="Z19">
         <v>1.42</v>
       </c>
-      <c r="S19">
-        <v>2.55</v>
-      </c>
-      <c r="T19">
-        <v>3.2</v>
-      </c>
-      <c r="U19">
-        <v>1.27</v>
-      </c>
-      <c r="V19">
-        <v>8.5</v>
-      </c>
-      <c r="W19">
-        <v>1.06</v>
-      </c>
-      <c r="X19">
-        <v>1.05</v>
-      </c>
-      <c r="Y19">
-        <v>7.1</v>
-      </c>
-      <c r="Z19">
-        <v>1.37</v>
-      </c>
       <c r="AA19">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AB19">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AC19">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AD19">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AE19">
         <v>1.17</v>
@@ -3880,72 +2926,18 @@
         <v>1.67</v>
       </c>
       <c r="AH19">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AI19">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AJ19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AK19" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL19">
-        <v>1.25</v>
-      </c>
-      <c r="AM19">
-        <v>1.27</v>
-      </c>
-      <c r="AN19">
-        <v>1.06</v>
-      </c>
-      <c r="AO19">
-        <v>-1</v>
-      </c>
-      <c r="AP19">
-        <v>1.44</v>
-      </c>
-      <c r="AQ19">
-        <v>1.72</v>
-      </c>
-      <c r="AR19">
-        <v>2.28</v>
-      </c>
-      <c r="AS19">
-        <v>2.88</v>
-      </c>
-      <c r="AT19">
-        <v>3.8</v>
-      </c>
-      <c r="AU19">
-        <v>2.6</v>
-      </c>
-      <c r="AV19">
-        <v>2</v>
-      </c>
-      <c r="AW19">
-        <v>1.6</v>
-      </c>
-      <c r="AX19">
-        <v>1.36</v>
-      </c>
-      <c r="AY19">
-        <v>1.22</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>2.34</v>
-      </c>
-      <c r="BC19">
-        <v>1.77</v>
-      </c>
-      <c r="BD19" s="3">
+        <v>118</v>
+      </c>
+      <c r="AL19" s="3">
         <v>45798.8125</v>
       </c>
     </row>

--- a/jogos_2025-05-21.xlsx
+++ b/jogos_2025-05-21.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,22 +1030,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="M5" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>2.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['31', '80']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2.05</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45798.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,23 +1288,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="M7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S7" t="n">
         <v>3.2</v>
       </c>
-      <c r="N7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="T7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="AA7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.44</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['31', '80']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45798.5</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="M12" t="n">
-        <v>3.33</v>
+        <v>3.39</v>
       </c>
       <c r="N12" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="O12" t="n">
         <v>2.8</v>
@@ -1974,40 +1974,40 @@
         <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="T12" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
         <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
         <v>1.62</v>
@@ -2017,25 +2017,25 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['19', '23', '38', '58']</t>
+          <t>['4', '30', '67', '86']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['5', '7', '53', '66']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" t="n">
         <v>1.85</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45798.58333333334</v>
@@ -2062,16 +2062,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2084,69 +2084,69 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,91 +2191,91 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['6', '45+1', '46', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45798.58333333334</v>
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,65 +2346,65 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.86</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.97</v>
+        <v>2.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.94</v>
+        <v>3.17</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
         <v>1.25</v>
       </c>
       <c r="X15" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="AB15" t="n">
         <v>1.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['4', '30', '67', '86']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>2.69</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2578,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.13</v>
+        <v>3.35</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="N17" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="O17" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
         <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="X17" t="n">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Z17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['34', '58']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['49', '61']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45798.64583333334</v>
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.35</v>
+        <v>3.13</v>
       </c>
       <c r="M18" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
         <v>2.65</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['49', '61']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.34</v>
       </c>
-      <c r="X18" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['34', '58']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['77']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AI18" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45798.64583333334</v>
@@ -2965,19 +2965,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Atlético Tembetary</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Guaraní</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="P20" t="n">
         <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="R20" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
         <v>1.42</v>
       </c>
       <c r="X20" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['54']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['28', '78']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
         <v>1.44</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45798.8125</v>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético Tembetary</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Guaraní</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O21" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="P21" t="n">
         <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="S21" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W21" t="n">
         <v>1.42</v>
       </c>
       <c r="X21" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AA21" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['28', '78']</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
         <v>1.44</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45798.8125</v>
